--- a/DEV/org.openl.rules.test/test-resources/functionality/Range-DoublePrefix.xlsx
+++ b/DEV/org.openl.rules.test/test-resources/functionality/Range-DoublePrefix.xlsx
@@ -119,604 +119,604 @@
     </r>
   </si>
   <si>
-    <t>&lt;=1K</t>
-  </si>
-  <si>
-    <t>&lt;=2K</t>
-  </si>
-  <si>
-    <t>&lt;=3K</t>
-  </si>
-  <si>
-    <t>&lt;=4K</t>
-  </si>
-  <si>
-    <t>&lt;=5K</t>
-  </si>
-  <si>
-    <t>&lt;=6K</t>
-  </si>
-  <si>
-    <t>&lt;=7K</t>
-  </si>
-  <si>
-    <t>&lt;=8K</t>
-  </si>
-  <si>
-    <t>&lt;=9K</t>
-  </si>
-  <si>
-    <t>&lt;=10K</t>
-  </si>
-  <si>
-    <t>&lt;=11K</t>
-  </si>
-  <si>
-    <t>&lt;=12K</t>
-  </si>
-  <si>
-    <t>&lt;=13K</t>
-  </si>
-  <si>
-    <t>&lt;=14K</t>
-  </si>
-  <si>
-    <t>&lt;=15K</t>
-  </si>
-  <si>
-    <t>&lt;=16K</t>
-  </si>
-  <si>
-    <t>&lt;=17K</t>
-  </si>
-  <si>
-    <t>&lt;=18K</t>
-  </si>
-  <si>
-    <t>&lt;=19K</t>
-  </si>
-  <si>
-    <t>&lt;=20K</t>
-  </si>
-  <si>
-    <t>&lt;=21K</t>
-  </si>
-  <si>
-    <t>&lt;=22K</t>
-  </si>
-  <si>
-    <t>&lt;=23K</t>
-  </si>
-  <si>
-    <t>&lt;=24K</t>
-  </si>
-  <si>
-    <t>&lt;=25K</t>
-  </si>
-  <si>
-    <t>&lt;=26K</t>
-  </si>
-  <si>
-    <t>&lt;=27K</t>
-  </si>
-  <si>
-    <t>&lt;=28K</t>
-  </si>
-  <si>
-    <t>&lt;=29K</t>
-  </si>
-  <si>
-    <t>&lt;=30K</t>
-  </si>
-  <si>
-    <t>&lt;=31K</t>
-  </si>
-  <si>
-    <t>&lt;=32K</t>
-  </si>
-  <si>
-    <t>&lt;=33K</t>
-  </si>
-  <si>
-    <t>&lt;=34K</t>
-  </si>
-  <si>
-    <t>&lt;=35K</t>
-  </si>
-  <si>
-    <t>&lt;=36K</t>
-  </si>
-  <si>
-    <t>&lt;=37K</t>
-  </si>
-  <si>
-    <t>&lt;=38K</t>
-  </si>
-  <si>
-    <t>&lt;=39K</t>
-  </si>
-  <si>
-    <t>&lt;=40K</t>
-  </si>
-  <si>
-    <t>&lt;=41K</t>
-  </si>
-  <si>
-    <t>&lt;=42K</t>
-  </si>
-  <si>
-    <t>&lt;=43K</t>
-  </si>
-  <si>
-    <t>&lt;=44K</t>
-  </si>
-  <si>
-    <t>&lt;=45K</t>
-  </si>
-  <si>
-    <t>&lt;=46K</t>
-  </si>
-  <si>
-    <t>&lt;=47K</t>
-  </si>
-  <si>
-    <t>&lt;=48K</t>
-  </si>
-  <si>
-    <t>&lt;=49K</t>
-  </si>
-  <si>
-    <t>&lt;=50K</t>
-  </si>
-  <si>
-    <t>&lt;=51K</t>
-  </si>
-  <si>
-    <t>&lt;=52K</t>
-  </si>
-  <si>
-    <t>&lt;=53K</t>
-  </si>
-  <si>
-    <t>&lt;=54K</t>
-  </si>
-  <si>
-    <t>&lt;=55K</t>
-  </si>
-  <si>
-    <t>&lt;=56K</t>
-  </si>
-  <si>
-    <t>&lt;=57K</t>
-  </si>
-  <si>
-    <t>&lt;=58K</t>
-  </si>
-  <si>
-    <t>&lt;=59K</t>
-  </si>
-  <si>
-    <t>&lt;=60K</t>
-  </si>
-  <si>
-    <t>&lt;=61K</t>
-  </si>
-  <si>
-    <t>&lt;=62K</t>
-  </si>
-  <si>
-    <t>&lt;=63K</t>
-  </si>
-  <si>
-    <t>&lt;=64K</t>
-  </si>
-  <si>
-    <t>&lt;=65K</t>
-  </si>
-  <si>
-    <t>&lt;=66K</t>
-  </si>
-  <si>
-    <t>&lt;=67K</t>
-  </si>
-  <si>
-    <t>&lt;=68K</t>
-  </si>
-  <si>
-    <t>&lt;=69K</t>
-  </si>
-  <si>
-    <t>&lt;=70K</t>
-  </si>
-  <si>
-    <t>&lt;=71K</t>
-  </si>
-  <si>
-    <t>&lt;=72K</t>
-  </si>
-  <si>
-    <t>&lt;=73K</t>
-  </si>
-  <si>
-    <t>&lt;=74K</t>
-  </si>
-  <si>
-    <t>&lt;=75K</t>
-  </si>
-  <si>
-    <t>&lt;=76K</t>
-  </si>
-  <si>
-    <t>&lt;=77K</t>
-  </si>
-  <si>
-    <t>&lt;=78K</t>
-  </si>
-  <si>
-    <t>&lt;=79K</t>
-  </si>
-  <si>
-    <t>&lt;=80K</t>
-  </si>
-  <si>
-    <t>&lt;=81K</t>
-  </si>
-  <si>
-    <t>&lt;=82K</t>
-  </si>
-  <si>
-    <t>&lt;=83K</t>
-  </si>
-  <si>
-    <t>&lt;=84K</t>
-  </si>
-  <si>
-    <t>&lt;=85K</t>
-  </si>
-  <si>
-    <t>&lt;=86K</t>
-  </si>
-  <si>
-    <t>&lt;=87K</t>
-  </si>
-  <si>
-    <t>&lt;=88K</t>
-  </si>
-  <si>
-    <t>&lt;=89K</t>
-  </si>
-  <si>
-    <t>&lt;=90K</t>
-  </si>
-  <si>
-    <t>&lt;=91K</t>
-  </si>
-  <si>
-    <t>&lt;=92K</t>
-  </si>
-  <si>
-    <t>&lt;=93K</t>
-  </si>
-  <si>
-    <t>&lt;=94K</t>
-  </si>
-  <si>
-    <t>&lt;=95K</t>
-  </si>
-  <si>
-    <t>&lt;=96K</t>
-  </si>
-  <si>
-    <t>&lt;=97K</t>
-  </si>
-  <si>
-    <t>&lt;=98K</t>
-  </si>
-  <si>
-    <t>&lt;=99K</t>
-  </si>
-  <si>
-    <t>&lt;=100K</t>
-  </si>
-  <si>
-    <t>&lt;=101K</t>
-  </si>
-  <si>
-    <t>&lt;=102K</t>
-  </si>
-  <si>
-    <t>&lt;=103K</t>
-  </si>
-  <si>
-    <t>&lt;=104K</t>
-  </si>
-  <si>
-    <t>&lt;=105K</t>
-  </si>
-  <si>
-    <t>&lt;=106K</t>
-  </si>
-  <si>
-    <t>&lt;=107K</t>
-  </si>
-  <si>
-    <t>&lt;=108K</t>
-  </si>
-  <si>
-    <t>&lt;=109K</t>
-  </si>
-  <si>
-    <t>&lt;=110K</t>
-  </si>
-  <si>
-    <t>&lt;=111K</t>
-  </si>
-  <si>
-    <t>&lt;=112K</t>
-  </si>
-  <si>
-    <t>&lt;=113K</t>
-  </si>
-  <si>
-    <t>&lt;=114K</t>
-  </si>
-  <si>
-    <t>&lt;=115K</t>
-  </si>
-  <si>
-    <t>&lt;=116K</t>
-  </si>
-  <si>
-    <t>&lt;=117K</t>
-  </si>
-  <si>
-    <t>&lt;=118K</t>
-  </si>
-  <si>
-    <t>&lt;=119K</t>
-  </si>
-  <si>
-    <t>&lt;=120K</t>
-  </si>
-  <si>
-    <t>&lt;=121K</t>
-  </si>
-  <si>
-    <t>&lt;=122K</t>
-  </si>
-  <si>
-    <t>&lt;=123K</t>
-  </si>
-  <si>
-    <t>&lt;=124K</t>
-  </si>
-  <si>
-    <t>&lt;=125K</t>
-  </si>
-  <si>
-    <t>&lt;=126K</t>
-  </si>
-  <si>
-    <t>&lt;=127K</t>
-  </si>
-  <si>
-    <t>&lt;=128K</t>
-  </si>
-  <si>
-    <t>&lt;=129K</t>
-  </si>
-  <si>
-    <t>&lt;=130K</t>
-  </si>
-  <si>
-    <t>&lt;=131K</t>
-  </si>
-  <si>
-    <t>&lt;=132K</t>
-  </si>
-  <si>
-    <t>&lt;=133K</t>
-  </si>
-  <si>
-    <t>&lt;=134K</t>
-  </si>
-  <si>
-    <t>&lt;=135K</t>
-  </si>
-  <si>
-    <t>&lt;=136K</t>
-  </si>
-  <si>
-    <t>&lt;=137K</t>
-  </si>
-  <si>
-    <t>&lt;=138K</t>
-  </si>
-  <si>
-    <t>&lt;=139K</t>
-  </si>
-  <si>
-    <t>&lt;=140K</t>
-  </si>
-  <si>
-    <t>&lt;=141K</t>
-  </si>
-  <si>
-    <t>&lt;=142K</t>
-  </si>
-  <si>
-    <t>&lt;=143K</t>
-  </si>
-  <si>
-    <t>&lt;=144K</t>
-  </si>
-  <si>
-    <t>&lt;=145K</t>
-  </si>
-  <si>
-    <t>&lt;=146K</t>
-  </si>
-  <si>
-    <t>&lt;=147K</t>
-  </si>
-  <si>
-    <t>&lt;=148K</t>
-  </si>
-  <si>
-    <t>&lt;=149K</t>
-  </si>
-  <si>
-    <t>&lt;=150K</t>
-  </si>
-  <si>
-    <t>&lt;=151K</t>
-  </si>
-  <si>
-    <t>&lt;=152K</t>
-  </si>
-  <si>
-    <t>&lt;=153K</t>
-  </si>
-  <si>
-    <t>&lt;=154K</t>
-  </si>
-  <si>
-    <t>&lt;=155K</t>
-  </si>
-  <si>
-    <t>&lt;=156K</t>
-  </si>
-  <si>
-    <t>&lt;=157K</t>
-  </si>
-  <si>
-    <t>&lt;=158K</t>
-  </si>
-  <si>
-    <t>&lt;=159K</t>
-  </si>
-  <si>
-    <t>&lt;=160K</t>
-  </si>
-  <si>
-    <t>&lt;=161K</t>
-  </si>
-  <si>
-    <t>&lt;=162K</t>
-  </si>
-  <si>
-    <t>&lt;=163K</t>
-  </si>
-  <si>
-    <t>&lt;=164K</t>
-  </si>
-  <si>
-    <t>&lt;=165K</t>
-  </si>
-  <si>
-    <t>&lt;=166K</t>
-  </si>
-  <si>
-    <t>&lt;=167K</t>
-  </si>
-  <si>
-    <t>&lt;=168K</t>
-  </si>
-  <si>
-    <t>&lt;=169K</t>
-  </si>
-  <si>
-    <t>&lt;=170K</t>
-  </si>
-  <si>
-    <t>&lt;=171K</t>
-  </si>
-  <si>
-    <t>&lt;=172K</t>
-  </si>
-  <si>
-    <t>&lt;=173K</t>
-  </si>
-  <si>
-    <t>&lt;=174K</t>
-  </si>
-  <si>
-    <t>&lt;=175K</t>
-  </si>
-  <si>
-    <t>&lt;=176K</t>
-  </si>
-  <si>
-    <t>&lt;=177K</t>
-  </si>
-  <si>
-    <t>&lt;=178K</t>
-  </si>
-  <si>
-    <t>&lt;=179K</t>
-  </si>
-  <si>
-    <t>&lt;=180K</t>
-  </si>
-  <si>
-    <t>&lt;=181K</t>
-  </si>
-  <si>
-    <t>&lt;=182K</t>
-  </si>
-  <si>
-    <t>&lt;=183K</t>
-  </si>
-  <si>
-    <t>&lt;=184K</t>
-  </si>
-  <si>
-    <t>&lt;=185K</t>
-  </si>
-  <si>
-    <t>&lt;=186K</t>
-  </si>
-  <si>
-    <t>&lt;=187K</t>
-  </si>
-  <si>
-    <t>&lt;=188K</t>
-  </si>
-  <si>
-    <t>&lt;=189K</t>
-  </si>
-  <si>
-    <t>&lt;=190K</t>
-  </si>
-  <si>
-    <t>&lt;=191K</t>
-  </si>
-  <si>
-    <t>&lt;=192K</t>
-  </si>
-  <si>
-    <t>&lt;=193K</t>
-  </si>
-  <si>
-    <t>&lt;=194K</t>
-  </si>
-  <si>
-    <t>&lt;=195K</t>
-  </si>
-  <si>
-    <t>&lt;=196K</t>
-  </si>
-  <si>
-    <t>&lt;=197K</t>
-  </si>
-  <si>
-    <t>&lt;=198K</t>
-  </si>
-  <si>
-    <t>&lt;=199K</t>
-  </si>
-  <si>
-    <t>&lt;=200K</t>
+    <t>&lt;=1000</t>
+  </si>
+  <si>
+    <t>&lt;=2000</t>
+  </si>
+  <si>
+    <t>&lt;=3000</t>
+  </si>
+  <si>
+    <t>&lt;=4000</t>
+  </si>
+  <si>
+    <t>&lt;=5000</t>
+  </si>
+  <si>
+    <t>&lt;=6000</t>
+  </si>
+  <si>
+    <t>&lt;=7000</t>
+  </si>
+  <si>
+    <t>&lt;=8000</t>
+  </si>
+  <si>
+    <t>&lt;=9000</t>
+  </si>
+  <si>
+    <t>&lt;=10000</t>
+  </si>
+  <si>
+    <t>&lt;=11000</t>
+  </si>
+  <si>
+    <t>&lt;=12000</t>
+  </si>
+  <si>
+    <t>&lt;=13000</t>
+  </si>
+  <si>
+    <t>&lt;=14000</t>
+  </si>
+  <si>
+    <t>&lt;=15000</t>
+  </si>
+  <si>
+    <t>&lt;=16000</t>
+  </si>
+  <si>
+    <t>&lt;=17000</t>
+  </si>
+  <si>
+    <t>&lt;=18000</t>
+  </si>
+  <si>
+    <t>&lt;=19000</t>
+  </si>
+  <si>
+    <t>&lt;=20000</t>
+  </si>
+  <si>
+    <t>&lt;=21000</t>
+  </si>
+  <si>
+    <t>&lt;=22000</t>
+  </si>
+  <si>
+    <t>&lt;=23000</t>
+  </si>
+  <si>
+    <t>&lt;=24000</t>
+  </si>
+  <si>
+    <t>&lt;=25000</t>
+  </si>
+  <si>
+    <t>&lt;=26000</t>
+  </si>
+  <si>
+    <t>&lt;=27000</t>
+  </si>
+  <si>
+    <t>&lt;=28000</t>
+  </si>
+  <si>
+    <t>&lt;=29000</t>
+  </si>
+  <si>
+    <t>&lt;=30000</t>
+  </si>
+  <si>
+    <t>&lt;=31000</t>
+  </si>
+  <si>
+    <t>&lt;=32000</t>
+  </si>
+  <si>
+    <t>&lt;=33000</t>
+  </si>
+  <si>
+    <t>&lt;=34000</t>
+  </si>
+  <si>
+    <t>&lt;=35000</t>
+  </si>
+  <si>
+    <t>&lt;=36000</t>
+  </si>
+  <si>
+    <t>&lt;=37000</t>
+  </si>
+  <si>
+    <t>&lt;=38000</t>
+  </si>
+  <si>
+    <t>&lt;=39000</t>
+  </si>
+  <si>
+    <t>&lt;=40000</t>
+  </si>
+  <si>
+    <t>&lt;=41000</t>
+  </si>
+  <si>
+    <t>&lt;=42000</t>
+  </si>
+  <si>
+    <t>&lt;=43000</t>
+  </si>
+  <si>
+    <t>&lt;=44000</t>
+  </si>
+  <si>
+    <t>&lt;=45000</t>
+  </si>
+  <si>
+    <t>&lt;=46000</t>
+  </si>
+  <si>
+    <t>&lt;=47000</t>
+  </si>
+  <si>
+    <t>&lt;=48000</t>
+  </si>
+  <si>
+    <t>&lt;=49000</t>
+  </si>
+  <si>
+    <t>&lt;=50000</t>
+  </si>
+  <si>
+    <t>&lt;=51000</t>
+  </si>
+  <si>
+    <t>&lt;=52000</t>
+  </si>
+  <si>
+    <t>&lt;=53000</t>
+  </si>
+  <si>
+    <t>&lt;=54000</t>
+  </si>
+  <si>
+    <t>&lt;=55000</t>
+  </si>
+  <si>
+    <t>&lt;=56000</t>
+  </si>
+  <si>
+    <t>&lt;=57000</t>
+  </si>
+  <si>
+    <t>&lt;=58000</t>
+  </si>
+  <si>
+    <t>&lt;=59000</t>
+  </si>
+  <si>
+    <t>&lt;=60000</t>
+  </si>
+  <si>
+    <t>&lt;=61000</t>
+  </si>
+  <si>
+    <t>&lt;=62000</t>
+  </si>
+  <si>
+    <t>&lt;=63000</t>
+  </si>
+  <si>
+    <t>&lt;=64000</t>
+  </si>
+  <si>
+    <t>&lt;=65000</t>
+  </si>
+  <si>
+    <t>&lt;=66000</t>
+  </si>
+  <si>
+    <t>&lt;=67000</t>
+  </si>
+  <si>
+    <t>&lt;=68000</t>
+  </si>
+  <si>
+    <t>&lt;=69000</t>
+  </si>
+  <si>
+    <t>&lt;=70000</t>
+  </si>
+  <si>
+    <t>&lt;=71000</t>
+  </si>
+  <si>
+    <t>&lt;=72000</t>
+  </si>
+  <si>
+    <t>&lt;=73000</t>
+  </si>
+  <si>
+    <t>&lt;=74000</t>
+  </si>
+  <si>
+    <t>&lt;=75000</t>
+  </si>
+  <si>
+    <t>&lt;=76000</t>
+  </si>
+  <si>
+    <t>&lt;=77000</t>
+  </si>
+  <si>
+    <t>&lt;=78000</t>
+  </si>
+  <si>
+    <t>&lt;=79000</t>
+  </si>
+  <si>
+    <t>&lt;=80000</t>
+  </si>
+  <si>
+    <t>&lt;=81000</t>
+  </si>
+  <si>
+    <t>&lt;=82000</t>
+  </si>
+  <si>
+    <t>&lt;=83000</t>
+  </si>
+  <si>
+    <t>&lt;=84000</t>
+  </si>
+  <si>
+    <t>&lt;=85000</t>
+  </si>
+  <si>
+    <t>&lt;=86000</t>
+  </si>
+  <si>
+    <t>&lt;=87000</t>
+  </si>
+  <si>
+    <t>&lt;=88000</t>
+  </si>
+  <si>
+    <t>&lt;=89000</t>
+  </si>
+  <si>
+    <t>&lt;=90000</t>
+  </si>
+  <si>
+    <t>&lt;=91000</t>
+  </si>
+  <si>
+    <t>&lt;=92000</t>
+  </si>
+  <si>
+    <t>&lt;=93000</t>
+  </si>
+  <si>
+    <t>&lt;=94000</t>
+  </si>
+  <si>
+    <t>&lt;=95000</t>
+  </si>
+  <si>
+    <t>&lt;=96000</t>
+  </si>
+  <si>
+    <t>&lt;=97000</t>
+  </si>
+  <si>
+    <t>&lt;=98000</t>
+  </si>
+  <si>
+    <t>&lt;=99000</t>
+  </si>
+  <si>
+    <t>&lt;=100000</t>
+  </si>
+  <si>
+    <t>&lt;=101000</t>
+  </si>
+  <si>
+    <t>&lt;=102000</t>
+  </si>
+  <si>
+    <t>&lt;=103000</t>
+  </si>
+  <si>
+    <t>&lt;=104000</t>
+  </si>
+  <si>
+    <t>&lt;=105000</t>
+  </si>
+  <si>
+    <t>&lt;=106000</t>
+  </si>
+  <si>
+    <t>&lt;=107000</t>
+  </si>
+  <si>
+    <t>&lt;=108000</t>
+  </si>
+  <si>
+    <t>&lt;=109000</t>
+  </si>
+  <si>
+    <t>&lt;=110000</t>
+  </si>
+  <si>
+    <t>&lt;=111000</t>
+  </si>
+  <si>
+    <t>&lt;=112000</t>
+  </si>
+  <si>
+    <t>&lt;=113000</t>
+  </si>
+  <si>
+    <t>&lt;=114000</t>
+  </si>
+  <si>
+    <t>&lt;=115000</t>
+  </si>
+  <si>
+    <t>&lt;=116000</t>
+  </si>
+  <si>
+    <t>&lt;=117000</t>
+  </si>
+  <si>
+    <t>&lt;=118000</t>
+  </si>
+  <si>
+    <t>&lt;=119000</t>
+  </si>
+  <si>
+    <t>&lt;=120000</t>
+  </si>
+  <si>
+    <t>&lt;=121000</t>
+  </si>
+  <si>
+    <t>&lt;=122000</t>
+  </si>
+  <si>
+    <t>&lt;=123000</t>
+  </si>
+  <si>
+    <t>&lt;=124000</t>
+  </si>
+  <si>
+    <t>&lt;=125000</t>
+  </si>
+  <si>
+    <t>&lt;=126000</t>
+  </si>
+  <si>
+    <t>&lt;=127000</t>
+  </si>
+  <si>
+    <t>&lt;=128000</t>
+  </si>
+  <si>
+    <t>&lt;=129000</t>
+  </si>
+  <si>
+    <t>&lt;=130000</t>
+  </si>
+  <si>
+    <t>&lt;=131000</t>
+  </si>
+  <si>
+    <t>&lt;=132000</t>
+  </si>
+  <si>
+    <t>&lt;=133000</t>
+  </si>
+  <si>
+    <t>&lt;=134000</t>
+  </si>
+  <si>
+    <t>&lt;=135000</t>
+  </si>
+  <si>
+    <t>&lt;=136000</t>
+  </si>
+  <si>
+    <t>&lt;=137000</t>
+  </si>
+  <si>
+    <t>&lt;=138000</t>
+  </si>
+  <si>
+    <t>&lt;=139000</t>
+  </si>
+  <si>
+    <t>&lt;=140000</t>
+  </si>
+  <si>
+    <t>&lt;=141000</t>
+  </si>
+  <si>
+    <t>&lt;=142000</t>
+  </si>
+  <si>
+    <t>&lt;=143000</t>
+  </si>
+  <si>
+    <t>&lt;=144000</t>
+  </si>
+  <si>
+    <t>&lt;=145000</t>
+  </si>
+  <si>
+    <t>&lt;=146000</t>
+  </si>
+  <si>
+    <t>&lt;=147000</t>
+  </si>
+  <si>
+    <t>&lt;=148000</t>
+  </si>
+  <si>
+    <t>&lt;=149000</t>
+  </si>
+  <si>
+    <t>&lt;=150000</t>
+  </si>
+  <si>
+    <t>&lt;=151000</t>
+  </si>
+  <si>
+    <t>&lt;=152000</t>
+  </si>
+  <si>
+    <t>&lt;=153000</t>
+  </si>
+  <si>
+    <t>&lt;=154000</t>
+  </si>
+  <si>
+    <t>&lt;=155000</t>
+  </si>
+  <si>
+    <t>&lt;=156000</t>
+  </si>
+  <si>
+    <t>&lt;=157000</t>
+  </si>
+  <si>
+    <t>&lt;=158000</t>
+  </si>
+  <si>
+    <t>&lt;=159000</t>
+  </si>
+  <si>
+    <t>&lt;=160000</t>
+  </si>
+  <si>
+    <t>&lt;=161000</t>
+  </si>
+  <si>
+    <t>&lt;=162000</t>
+  </si>
+  <si>
+    <t>&lt;=163000</t>
+  </si>
+  <si>
+    <t>&lt;=164000</t>
+  </si>
+  <si>
+    <t>&lt;=165000</t>
+  </si>
+  <si>
+    <t>&lt;=166000</t>
+  </si>
+  <si>
+    <t>&lt;=167000</t>
+  </si>
+  <si>
+    <t>&lt;=168000</t>
+  </si>
+  <si>
+    <t>&lt;=169000</t>
+  </si>
+  <si>
+    <t>&lt;=170000</t>
+  </si>
+  <si>
+    <t>&lt;=171000</t>
+  </si>
+  <si>
+    <t>&lt;=172000</t>
+  </si>
+  <si>
+    <t>&lt;=173000</t>
+  </si>
+  <si>
+    <t>&lt;=174000</t>
+  </si>
+  <si>
+    <t>&lt;=175000</t>
+  </si>
+  <si>
+    <t>&lt;=176000</t>
+  </si>
+  <si>
+    <t>&lt;=177000</t>
+  </si>
+  <si>
+    <t>&lt;=178000</t>
+  </si>
+  <si>
+    <t>&lt;=179000</t>
+  </si>
+  <si>
+    <t>&lt;=180000</t>
+  </si>
+  <si>
+    <t>&lt;=181000</t>
+  </si>
+  <si>
+    <t>&lt;=182000</t>
+  </si>
+  <si>
+    <t>&lt;=183000</t>
+  </si>
+  <si>
+    <t>&lt;=184000</t>
+  </si>
+  <si>
+    <t>&lt;=185000</t>
+  </si>
+  <si>
+    <t>&lt;=186000</t>
+  </si>
+  <si>
+    <t>&lt;=187000</t>
+  </si>
+  <si>
+    <t>&lt;=188000</t>
+  </si>
+  <si>
+    <t>&lt;=189000</t>
+  </si>
+  <si>
+    <t>&lt;=190000</t>
+  </si>
+  <si>
+    <t>&lt;=191000</t>
+  </si>
+  <si>
+    <t>&lt;=192000</t>
+  </si>
+  <si>
+    <t>&lt;=193000</t>
+  </si>
+  <si>
+    <t>&lt;=194000</t>
+  </si>
+  <si>
+    <t>&lt;=195000</t>
+  </si>
+  <si>
+    <t>&lt;=196000</t>
+  </si>
+  <si>
+    <t>&lt;=197000</t>
+  </si>
+  <si>
+    <t>&lt;=198000</t>
+  </si>
+  <si>
+    <t>&lt;=199000</t>
+  </si>
+  <si>
+    <t>&lt;=200000</t>
   </si>
 </sst>
 </file>
